--- a/outputs/05_benchmark_signals/tables_v_viii/us/table_vii_return_logit.xlsx
+++ b/outputs/05_benchmark_signals/tables_v_viii/us/table_vii_return_logit.xlsx
@@ -472,35 +472,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.00*** (7.4)</t>
+          <t>2.02*** (7.7)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.00*** (8.5)</t>
+          <t>1.85*** (9.6)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.00*** (11.2)</t>
+          <t>2.56*** (12.6)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.00*** (9.7)</t>
+          <t>1.69*** (10.9)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.00*** (10.5)</t>
+          <t>2.98*** (11.0)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.00*** (6.5)</t>
+          <t>1.16*** (6.8)</t>
         </is>
       </c>
     </row>
@@ -513,34 +513,34 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.00 (1.1)</t>
+          <t>0.04 (1.0)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.00 (1.0)</t>
+          <t>0.04 (0.9)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.00 (1.1)</t>
+          <t>0.04 (1.0)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.00 (1.1)</t>
+          <t>0.05 (1.0)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.00 (1.1)</t>
+          <t>0.04 (1.0)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.00 (1.0)</t>
+          <t>0.04 (0.9)</t>
         </is>
       </c>
     </row>
@@ -553,34 +553,34 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.00 (0.4)</t>
+          <t>0.02 (0.5)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.00 (0.2)</t>
+          <t>0.00 (0.1)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.00 (0.4)</t>
+          <t>0.02 (0.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>0.04 (1.2)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.00 (0.4)</t>
+          <t>0.02 (0.5)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>0.02 (0.6)</t>
         </is>
       </c>
     </row>
@@ -593,34 +593,34 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.00*** (2.7)</t>
+          <t>0.13*** (3.9)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00** (2.2)</t>
+          <t>-0.13** (-2.6)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.00*** (2.7)</t>
+          <t>0.13*** (3.9)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.00** (2.5)</t>
+          <t>-0.09** (-2.4)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.00*** (2.7)</t>
+          <t>0.13*** (3.9)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.00** (2.5)</t>
+          <t>-0.03 (-0.8)</t>
         </is>
       </c>
     </row>
@@ -633,34 +633,34 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.00*** (7.9)</t>
+          <t>0.30*** (8.4)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00*** (7.3)</t>
+          <t>0.24*** (7.3)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.00*** (7.9)</t>
+          <t>0.30*** (8.4)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.00*** (7.4)</t>
+          <t>0.24*** (7.4)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.00*** (7.9)</t>
+          <t>0.30*** (8.4)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.00*** (7.9)</t>
+          <t>0.29*** (8.3)</t>
         </is>
       </c>
     </row>
@@ -673,34 +673,34 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.00 (-0.2)</t>
+          <t>-0.01 (-0.1)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>-0.02 (-0.2)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.00 (-0.2)</t>
+          <t>-0.01 (-0.1)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>-0.02 (-0.2)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.00 (-0.2)</t>
+          <t>-0.01 (-0.1)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.00 (-0.2)</t>
+          <t>-0.01 (-0.1)</t>
         </is>
       </c>
     </row>
@@ -713,34 +713,34 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.00*** (-6.4)</t>
+          <t>-0.40*** (-6.4)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.00*** (-6.1)</t>
+          <t>-0.37*** (-6.1)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.00*** (-6.4)</t>
+          <t>-0.40*** (-6.4)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.00*** (-5.6)</t>
+          <t>-0.35*** (-5.6)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.00*** (-6.4)</t>
+          <t>-0.40*** (-6.4)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.00*** (-6.1)</t>
+          <t>-0.37*** (-6.1)</t>
         </is>
       </c>
     </row>
@@ -753,34 +753,34 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.00*** (3.3)</t>
+          <t>0.15*** (3.3)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.00*** (3.6)</t>
+          <t>0.17*** (3.5)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.00*** (3.3)</t>
+          <t>0.15*** (3.3)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.00*** (3.0)</t>
+          <t>0.14*** (3.0)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.00*** (3.3)</t>
+          <t>0.15*** (3.3)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.00*** (2.6)</t>
+          <t>0.12** (2.5)</t>
         </is>
       </c>
     </row>
@@ -793,34 +793,34 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.00 (0.3)</t>
+          <t>0.02 (0.3)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.00 (-1.2)</t>
+          <t>-0.08 (-1.3)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.00 (0.3)</t>
+          <t>0.02 (0.3)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.00** (-2.0)</t>
+          <t>-0.14** (-2.3)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.00 (0.3)</t>
+          <t>0.02 (0.3)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.00 (-0.9)</t>
+          <t>-0.06 (-1.0)</t>
         </is>
       </c>
     </row>
@@ -833,34 +833,34 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.00 (1.5)</t>
+          <t>0.04 (1.5)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.00 (1.4)</t>
+          <t>-0.18*** (-4.2)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.00 (1.5)</t>
+          <t>0.04 (1.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.00* (1.7)</t>
+          <t>-0.15*** (-4.3)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.00 (1.5)</t>
+          <t>0.04 (1.5)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.00 (1.5)</t>
+          <t>-0.10*** (-2.6)</t>
         </is>
       </c>
     </row>
@@ -873,34 +873,34 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.00* (-1.8)</t>
+          <t>-0.12* (-1.7)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.00* (-1.9)</t>
+          <t>-0.13* (-1.9)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.00* (-1.8)</t>
+          <t>-0.12* (-1.7)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.00* (-1.9)</t>
+          <t>-0.13* (-1.9)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.00* (-1.8)</t>
+          <t>-0.12* (-1.7)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.00* (-1.8)</t>
+          <t>-0.12* (-1.8)</t>
         </is>
       </c>
     </row>
@@ -913,34 +913,34 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.00** (-2.3)</t>
+          <t>-0.20** (-2.3)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.3)</t>
+          <t>-0.30*** (-3.5)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.00** (-2.3)</t>
+          <t>-0.20** (-2.3)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.8)</t>
+          <t>-0.34*** (-4.0)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.00** (-2.3)</t>
+          <t>-0.20** (-2.3)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.0)</t>
+          <t>-0.26*** (-3.1)</t>
         </is>
       </c>
     </row>
@@ -953,34 +953,34 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.00 (0.2)</t>
+          <t>-0.04 (-1.4)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>-0.24*** (-5.5)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.00 (0.2)</t>
+          <t>-0.04 (-1.4)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>-0.20*** (-5.6)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.00 (0.2)</t>
+          <t>-0.04 (-1.4)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.00 (0.5)</t>
+          <t>-0.16*** (-4.1)</t>
         </is>
       </c>
     </row>
@@ -1113,46 +1113,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.614227100374834e-05</v>
+        <v>2.02470304411708</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>5.152175073599267e-05</v>
+        <v>1.853633474772152</v>
       </c>
       <c r="E2" t="n">
-        <v>6.003388786620506e-05</v>
+        <v>2.562972768482822</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>5.094785467404634e-05</v>
+        <v>1.691363884739326</v>
       </c>
       <c r="H2" t="n">
-        <v>5.789702687749003e-05</v>
+        <v>2.982467323895681</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>3.097155307266168e-05</v>
+        <v>1.164846663015449</v>
       </c>
       <c r="K2" t="n">
-        <v>7.385273217649249</v>
+        <v>7.684748064674315</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>8.458765940215345</v>
+        <v>9.56365745087804</v>
       </c>
       <c r="N2" t="n">
-        <v>11.21215551390705</v>
+        <v>12.600504601029</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>9.679609225316451</v>
+        <v>10.94283430028991</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.49502007136554</v>
+        <v>11.049871433321</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>6.531067782624302</v>
+        <v>6.755092653465997</v>
       </c>
     </row>
     <row r="3">
@@ -1163,45 +1163,45 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1.006133285632135e-05</v>
+        <v>0.04332110316317771</v>
       </c>
       <c r="D3" t="n">
-        <v>9.31295278340065e-06</v>
+        <v>0.03900046252086963</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>1.006133285632135e-05</v>
+        <v>0.04332110316317771</v>
       </c>
       <c r="G3" t="n">
-        <v>1.068987887769643e-05</v>
+        <v>0.04578300999145297</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>1.006133285632135e-05</v>
+        <v>0.04332110316317771</v>
       </c>
       <c r="J3" t="n">
-        <v>9.842627650310403e-06</v>
+        <v>0.04167350907653614</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>1.053329012949879</v>
+        <v>0.9506264350669853</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9731131080568303</v>
+        <v>0.8514529900452821</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>1.053329012949879</v>
+        <v>0.9506264350669853</v>
       </c>
       <c r="P3" t="n">
-        <v>1.121047661067511</v>
+        <v>1.003951467003276</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>1.053329012949879</v>
+        <v>0.9506264350669853</v>
       </c>
       <c r="S3" t="n">
-        <v>1.036050411592944</v>
+        <v>0.91883587284504</v>
       </c>
     </row>
     <row r="4">
@@ -1212,45 +1212,45 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>3.30496977288338e-06</v>
+        <v>0.01599540628255555</v>
       </c>
       <c r="D4" t="n">
-        <v>1.126806993907227e-06</v>
+        <v>0.004758507117013159</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>3.30496977288338e-06</v>
+        <v>0.01599540628255555</v>
       </c>
       <c r="G4" t="n">
-        <v>8.721840916608687e-06</v>
+        <v>0.04170386986609272</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>3.30496977288338e-06</v>
+        <v>0.01599540628255555</v>
       </c>
       <c r="J4" t="n">
-        <v>4.572918413347327e-06</v>
+        <v>0.02009579617005213</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.4404258492200654</v>
+        <v>0.450662248940429</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1515354083426846</v>
+        <v>0.1347055223886542</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>0.4404258492200654</v>
+        <v>0.450662248940429</v>
       </c>
       <c r="P4" t="n">
-        <v>1.172157451197153</v>
+        <v>1.182124960001857</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>0.4404258492200654</v>
+        <v>0.450662248940429</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6176819372130493</v>
+        <v>0.573511617022457</v>
       </c>
     </row>
     <row r="5">
@@ -1261,45 +1261,45 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>4.013105358479088e-05</v>
+        <v>0.1300298060710949</v>
       </c>
       <c r="D5" t="n">
-        <v>3.308576649350801e-05</v>
+        <v>-0.1264751739613219</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>4.013105358479088e-05</v>
+        <v>0.1300298060710949</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6632392689376e-05</v>
+        <v>-0.09304600923085016</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>4.013105358479088e-05</v>
+        <v>0.1300298060710949</v>
       </c>
       <c r="J5" t="n">
-        <v>3.607615353924334e-05</v>
+        <v>-0.03062193180303304</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>2.706154038761663</v>
+        <v>3.887852947310913</v>
       </c>
       <c r="M5" t="n">
-        <v>2.16629332917898</v>
+        <v>-2.573843832793209</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>2.706154038761663</v>
+        <v>3.887852947310913</v>
       </c>
       <c r="P5" t="n">
-        <v>2.479208848308944</v>
+        <v>-2.374090982885181</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>2.706154038761663</v>
+        <v>3.887852947310913</v>
       </c>
       <c r="S5" t="n">
-        <v>2.464858736827349</v>
+        <v>-0.7617187650841966</v>
       </c>
     </row>
     <row r="6">
@@ -1310,45 +1310,45 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>6.697286558608074e-05</v>
+        <v>0.2999889569821954</v>
       </c>
       <c r="D6" t="n">
-        <v>5.403265805779725e-05</v>
+        <v>0.2353365646542792</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>6.697286558608074e-05</v>
+        <v>0.2999889569821954</v>
       </c>
       <c r="G6" t="n">
-        <v>5.579066553984711e-05</v>
+        <v>0.2427529628379867</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>6.697286558608074e-05</v>
+        <v>0.2999889569821954</v>
       </c>
       <c r="J6" t="n">
-        <v>6.424372463035172e-05</v>
+        <v>0.2865734174206942</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>7.922769868517907</v>
+        <v>8.387311687725637</v>
       </c>
       <c r="M6" t="n">
-        <v>7.329241504018979</v>
+        <v>7.333029444057805</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>7.922769868517907</v>
+        <v>8.387311687725637</v>
       </c>
       <c r="P6" t="n">
-        <v>7.372602034832023</v>
+        <v>7.436103282107868</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>7.922769868517907</v>
+        <v>8.387311687725637</v>
       </c>
       <c r="S6" t="n">
-        <v>7.933757206080297</v>
+        <v>8.30846822018021</v>
       </c>
     </row>
     <row r="7">
@@ -1359,45 +1359,45 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>-3.363898110570893e-06</v>
+        <v>-0.006993621759993997</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.897205019570758e-06</v>
+        <v>-0.01931236218906634</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>-3.363898110570893e-06</v>
+        <v>-0.006993621759993997</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.379015636114189e-06</v>
+        <v>-0.01625134340489727</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>-3.363898110570893e-06</v>
+        <v>-0.006993621759993997</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.009476199230386e-06</v>
+        <v>-0.009748336325232962</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-0.1726059552388757</v>
+        <v>-0.0773025977171661</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3066526935856203</v>
+        <v>-0.2173163037646439</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>-0.1726059552388757</v>
+        <v>-0.0773025977171661</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2792257988102504</v>
+        <v>-0.1824133207284722</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>-0.1726059552388757</v>
+        <v>-0.0773025977171661</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2091942999550833</v>
+        <v>-0.1096118786891153</v>
       </c>
     </row>
     <row r="8">
@@ -1408,45 +1408,45 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>-8.563872213200421e-05</v>
+        <v>-0.3979882032140284</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.073239145753208e-05</v>
+        <v>-0.3730113328252862</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>-8.563872213200421e-05</v>
+        <v>-0.3979882032140284</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.503859926363491e-05</v>
+        <v>-0.3451193486415127</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>-8.563872213200421e-05</v>
+        <v>-0.3979882032140284</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.027103758947657e-05</v>
+        <v>-0.3719427962190751</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>-6.407958937526428</v>
+        <v>-6.401835611522368</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.085092820785801</v>
+        <v>-6.055046489526995</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>-6.407958937526428</v>
+        <v>-6.401835611522368</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.631255953476246</v>
+        <v>-5.56162490131607</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>-6.407958937526428</v>
+        <v>-6.401835611522368</v>
       </c>
       <c r="S8" t="n">
-        <v>-6.131406546964385</v>
+        <v>-6.112857180472397</v>
       </c>
     </row>
     <row r="9">
@@ -1457,45 +1457,45 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>3.311744935676926e-05</v>
+        <v>0.1549631481427458</v>
       </c>
       <c r="D9" t="n">
-        <v>3.523824960184893e-05</v>
+        <v>0.1653801639912914</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>3.311744935676926e-05</v>
+        <v>0.1549631481427458</v>
       </c>
       <c r="G9" t="n">
-        <v>2.98324770305068e-05</v>
+        <v>0.1384649530668627</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>3.311744935676926e-05</v>
+        <v>0.1549631481427458</v>
       </c>
       <c r="J9" t="n">
-        <v>2.523792103744146e-05</v>
+        <v>0.1157309674431687</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>3.337946542313627</v>
+        <v>3.295565141914636</v>
       </c>
       <c r="M9" t="n">
-        <v>3.551831459016491</v>
+        <v>3.512578685085776</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>3.337946542313627</v>
+        <v>3.295565141914636</v>
       </c>
       <c r="P9" t="n">
-        <v>3.023393266526998</v>
+        <v>2.956938065529602</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>3.337946542313627</v>
+        <v>3.295565141914636</v>
       </c>
       <c r="S9" t="n">
-        <v>2.615546219989832</v>
+        <v>2.514529277636585</v>
       </c>
     </row>
     <row r="10">
@@ -1506,45 +1506,45 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3.211514644116601e-06</v>
+        <v>0.01838092274278614</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.531070346757824e-05</v>
+        <v>-0.08067079270986245</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>3.211514644116601e-06</v>
+        <v>0.01838092274278614</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.730228863497003e-05</v>
+        <v>-0.140710542142716</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>3.211514644116601e-06</v>
+        <v>0.01838092274278614</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.188252823077832e-05</v>
+        <v>-0.05805327877878829</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>0.2512839005005197</v>
+        <v>0.3067714759178223</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.189775578722361</v>
+        <v>-1.343381869035032</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>0.2512839005005197</v>
+        <v>0.3067714759178223</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.045843351672297</v>
+        <v>-2.281754664454994</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>0.2512839005005197</v>
+        <v>0.3067714759178223</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.917535496509748</v>
+        <v>-0.9615182934758271</v>
       </c>
     </row>
     <row r="11">
@@ -1555,45 +1555,45 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2.12976239776915e-05</v>
+        <v>0.04274563538582424</v>
       </c>
       <c r="D11" t="n">
-        <v>2.054937906098864e-05</v>
+        <v>-0.1816919364256827</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>2.12976239776915e-05</v>
+        <v>0.04274563538582424</v>
       </c>
       <c r="G11" t="n">
-        <v>2.409701330471196e-05</v>
+        <v>-0.1483530256911058</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>2.12976239776915e-05</v>
+        <v>0.04274563538582424</v>
       </c>
       <c r="J11" t="n">
-        <v>2.129799569180042e-05</v>
+        <v>-0.097586533158616</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>1.487478772804806</v>
+        <v>1.472884029655878</v>
       </c>
       <c r="M11" t="n">
-        <v>1.42311714057456</v>
+        <v>-4.192147161160629</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>1.487478772804806</v>
+        <v>1.472884029655878</v>
       </c>
       <c r="P11" t="n">
-        <v>1.704270505631131</v>
+        <v>-4.311105827460791</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>1.487478772804806</v>
+        <v>1.472884029655878</v>
       </c>
       <c r="S11" t="n">
-        <v>1.515420899277931</v>
+        <v>-2.627994015034585</v>
       </c>
     </row>
     <row r="12">
@@ -1604,45 +1604,45 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>-2.570949578972964e-05</v>
+        <v>-0.1186381241339483</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.751963236249049e-05</v>
+        <v>-0.1287079468155436</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>-2.570949578972964e-05</v>
+        <v>-0.1186381241339483</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.737274336161953e-05</v>
+        <v>-0.1251346462724755</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>-2.570949578972964e-05</v>
+        <v>-0.1186381241339483</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.571235884191984e-05</v>
+        <v>-0.119187505590884</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>-1.75541377123095</v>
+        <v>-1.720970439866309</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.91286790470396</v>
+        <v>-1.916774530302625</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>-1.75541377123095</v>
+        <v>-1.720970439866309</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.894317098832213</v>
+        <v>-1.853509220141629</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>-1.75541377123095</v>
+        <v>-1.720970439866309</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.775414844368924</v>
+        <v>-1.753217121386347</v>
       </c>
     </row>
     <row r="13">
@@ -1653,45 +1653,45 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>-4.277813173367792e-05</v>
+        <v>-0.2018156023464363</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.016568886499063e-05</v>
+        <v>-0.2969187141848017</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>-4.277813173367792e-05</v>
+        <v>-0.2018156023464363</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.001500132560412e-05</v>
+        <v>-0.3421921261163272</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>-4.277813173367792e-05</v>
+        <v>-0.2018156023464363</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.367072645975319e-05</v>
+        <v>-0.2571384143064851</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-2.316906084477588</v>
+        <v>-2.344335319088887</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.312674284206656</v>
+        <v>-3.526022670111518</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>-2.316906084477588</v>
+        <v>-2.344335319088887</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.758297322830776</v>
+        <v>-3.97791060775241</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>-2.316906084477588</v>
+        <v>-2.344335319088887</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.980304951174567</v>
+        <v>-3.068949445770132</v>
       </c>
     </row>
     <row r="14">
@@ -1702,45 +1702,45 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>2.464194370590391e-06</v>
+        <v>-0.04453853529944116</v>
       </c>
       <c r="D14" t="n">
-        <v>8.012991628474926e-06</v>
+        <v>-0.2369086988900244</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2.464194370590391e-06</v>
+        <v>-0.04453853529944116</v>
       </c>
       <c r="G14" t="n">
-        <v>1.156163392004992e-05</v>
+        <v>-0.2036600421513646</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>2.464194370590391e-06</v>
+        <v>-0.04453853529944116</v>
       </c>
       <c r="J14" t="n">
-        <v>6.519837844360514e-06</v>
+        <v>-0.1645511345141974</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>0.1690340780542354</v>
+        <v>-1.355971569923656</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5582126775475463</v>
+        <v>-5.490468202790953</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>0.1690340780542354</v>
+        <v>-1.355971569923656</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8136041436567629</v>
+        <v>-5.640556636402785</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>0.1690340780542354</v>
+        <v>-1.355971569923656</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4592995342824345</v>
+        <v>-4.095351654500155</v>
       </c>
     </row>
     <row r="15">

--- a/outputs/05_benchmark_signals/tables_v_viii/us/table_vii_return_logit.xlsx
+++ b/outputs/05_benchmark_signals/tables_v_viii/us/table_vii_return_logit.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="display" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="display_stars" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1011,6 +1012,603 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>I5_R5_CNN</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>I5_R5_Chars</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>I5_R5_Joint</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>I20_R5_CNN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>I20_R5_Chars</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>I20_R5_Joint</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>I60_R5_CNN</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>I60_R5_Chars</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>I60_R5_Joint</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.02***</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.85***</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2.56***</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1.69***</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2.98***</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1.16***</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MOM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WSTR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.13***</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-0.13**</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.13***</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-0.09**</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.13***</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TREND</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.30***</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.24***</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.30***</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.24***</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.30***</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.29***</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Volat.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-0.40***</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-0.37***</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-0.40***</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-0.35***</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-0.40***</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-0.37***</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>52WH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.15***</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.17***</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.15***</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.14***</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.15***</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.12**</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dollar Volume</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-0.14**</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Zero Trade</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-0.18***</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-0.15***</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-0.10***</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-0.12*</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-0.13*</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-0.12*</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-0.13*</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.12*</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-0.12*</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Illiq.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-0.20**</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-0.30***</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-0.20**</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-0.34***</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-0.20**</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-0.26***</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lag Weekly Return</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-0.24***</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-0.20***</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-0.16***</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OOS McFadden R²</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/outputs/05_benchmark_signals/tables_v_viii/us/table_vii_return_logit.xlsx
+++ b/outputs/05_benchmark_signals/tables_v_viii/us/table_vii_return_logit.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.02*** (7.7)</t>
+          <t>2.08*** (6.2)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -484,7 +484,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.56*** (12.6)</t>
+          <t>2.57*** (10.6)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -495,7 +495,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.98*** (11.0)</t>
+          <t>2.88*** (10.0)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.02***</t>
+          <t>2.08***</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.56***</t>
+          <t>2.57***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.98***</t>
+          <t>2.88***</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -1711,42 +1711,42 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.02470304411708</v>
+        <v>2.077145367012783</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>1.853633474772152</v>
       </c>
       <c r="E2" t="n">
-        <v>2.562972768482822</v>
+        <v>2.565785835392407</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>1.691363884739326</v>
       </c>
       <c r="H2" t="n">
-        <v>2.982467323895681</v>
+        <v>2.877331715784794</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>1.164846663015449</v>
       </c>
       <c r="K2" t="n">
-        <v>7.684748064674315</v>
+        <v>6.180669798574272</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>9.56365745087804</v>
       </c>
       <c r="N2" t="n">
-        <v>12.600504601029</v>
+        <v>10.59507338917834</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>10.94283430028991</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.049871433321</v>
+        <v>10.01974611260875</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
